--- a/UV-Vis/Plots/Summary_Bandgaps.xlsx
+++ b/UV-Vis/Plots/Summary_Bandgaps.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.818063294318231</v>
+        <v>4.195021070897749</v>
       </c>
     </row>
     <row r="3">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.424397396537707</v>
+        <v>3.471451315540646</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.663892006679422</v>
+        <v>4.217863658797395</v>
       </c>
     </row>
     <row r="5">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.259553728182039</v>
+        <v>3.567594093766464</v>
       </c>
     </row>
     <row r="6">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2.414828072600478</v>
+        <v>4.260860116398623</v>
       </c>
     </row>
     <row r="7">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.2706240899692778</v>
+        <v>3.738655003122347</v>
       </c>
     </row>
   </sheetData>

--- a/UV-Vis/Plots/Summary_Bandgaps.xlsx
+++ b/UV-Vis/Plots/Summary_Bandgaps.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4.195021070897749</v>
+        <v>2.818063294318231</v>
       </c>
     </row>
     <row r="3">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3.471451315540646</v>
+        <v>1.424397396537707</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4.217863658797395</v>
+        <v>2.663892006679422</v>
       </c>
     </row>
     <row r="5">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3.567594093766464</v>
+        <v>1.259553728182039</v>
       </c>
     </row>
     <row r="6">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4.260860116398623</v>
+        <v>2.414828072600478</v>
       </c>
     </row>
     <row r="7">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.738655003122347</v>
+        <v>0.2706240899692778</v>
       </c>
     </row>
   </sheetData>

--- a/UV-Vis/Plots/Summary_Bandgaps.xlsx
+++ b/UV-Vis/Plots/Summary_Bandgaps.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CdS1</t>
+          <t>Sb2Se3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -445,13 +445,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.818063294318231</v>
+        <v>1.223375966444885</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CdS1</t>
+          <t>Sb2Se3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -460,67 +460,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.424397396537707</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CdS2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>2.663892006679422</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CdS2</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Indirect</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1.259553728182039</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CdS3</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2.414828072600478</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CdS3</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Indirect</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0.2706240899692778</v>
+        <v>1.204369530932377</v>
       </c>
     </row>
   </sheetData>

--- a/UV-Vis/Plots/Summary_Bandgaps.xlsx
+++ b/UV-Vis/Plots/Summary_Bandgaps.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sb2Se3</t>
+          <t>CdS1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -445,13 +445,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.223375966444885</v>
+        <v>2.238377246593132</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sb2Se3</t>
+          <t>CdS1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -460,7 +460,67 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.204369530932377</v>
+        <v>1.424397396537707</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CdS2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2.12008437563834</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CdS2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1.259553728182039</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CdS3</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1.962366367582087</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CdS3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.1666805568747302</v>
       </c>
     </row>
   </sheetData>

--- a/UV-Vis/Plots/Summary_Bandgaps.xlsx
+++ b/UV-Vis/Plots/Summary_Bandgaps.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CdS1</t>
+          <t>Sb2Se3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -445,13 +445,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.238377246593132</v>
+        <v>1.223375966444885</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CdS1</t>
+          <t>Sb2Se3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -460,67 +460,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.424397396537707</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CdS2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>2.12008437563834</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CdS2</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Indirect</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1.259553728182039</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CdS3</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1.962366367582087</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CdS3</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Indirect</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0.1666805568747302</v>
+        <v>1.204369530932377</v>
       </c>
     </row>
   </sheetData>

--- a/UV-Vis/Plots/Summary_Bandgaps.xlsx
+++ b/UV-Vis/Plots/Summary_Bandgaps.xlsx
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sb2Se3</t>
+          <t>Sheet1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -445,13 +445,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.223375966444885</v>
+        <v>1.190501355433966</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sb2Se3</t>
+          <t>Sheet1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.203027132367621</v>
+        <v>1.110128237447043</v>
       </c>
     </row>
   </sheetData>
